--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.38703604041925</v>
+        <v>7.050393356568129</v>
       </c>
       <c r="D2" t="n">
-        <v>52.80216527178651</v>
+        <v>8.58035185666531</v>
       </c>
       <c r="E2" t="n">
-        <v>6.095940458470746</v>
+        <v>0.9905903245014963</v>
       </c>
       <c r="F2" t="n">
-        <v>7.435404194608305</v>
+        <v>1.20825318162385</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.41432228586319</v>
+        <v>8.029827371452768</v>
       </c>
       <c r="D3" t="n">
-        <v>49.48708087811502</v>
+        <v>8.041650642693691</v>
       </c>
       <c r="E3" t="n">
-        <v>6.095940458470746</v>
+        <v>0.9905903245014963</v>
       </c>
       <c r="F3" t="n">
-        <v>7.435404194608305</v>
+        <v>1.20825318162385</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.17016714453479</v>
+        <v>5.227652160986903</v>
       </c>
       <c r="D4" t="n">
-        <v>32.54621815613685</v>
+        <v>5.288760450372237</v>
       </c>
       <c r="E4" t="n">
-        <v>6.095940458470746</v>
+        <v>0.9905903245014963</v>
       </c>
       <c r="F4" t="n">
-        <v>7.435404194608305</v>
+        <v>1.20825318162385</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.95451270413079</v>
+        <v>7.630108314421254</v>
       </c>
       <c r="D5" t="n">
-        <v>47.42450285950821</v>
+        <v>7.706481714670084</v>
       </c>
       <c r="E5" t="n">
-        <v>6.095940458470746</v>
+        <v>0.9905903245014963</v>
       </c>
       <c r="F5" t="n">
-        <v>7.435404194608305</v>
+        <v>1.20825318162385</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.1757507057975</v>
+        <v>6.366059489692094</v>
       </c>
       <c r="D6" t="n">
-        <v>38.88288260734013</v>
+        <v>6.318468423692771</v>
       </c>
       <c r="E6" t="n">
-        <v>6.095940458470746</v>
+        <v>0.9905903245014963</v>
       </c>
       <c r="F6" t="n">
-        <v>7.435404194608305</v>
+        <v>1.20825318162385</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
